--- a/output/roomself_excel/491.xlsx
+++ b/output/roomself_excel/491.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56420</v>
+        <v>115784</v>
       </c>
       <c r="D2" t="n">
-        <v>1908</v>
+        <v>2724</v>
       </c>
       <c r="E2" t="n">
-        <v>282</v>
+        <v>376</v>
       </c>
       <c r="F2" t="n">
-        <v>239</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>270133</v>
+        <v>200464</v>
       </c>
       <c r="D3" t="n">
-        <v>5608</v>
+        <v>3756</v>
       </c>
       <c r="E3" t="n">
-        <v>844</v>
+        <v>605</v>
       </c>
       <c r="F3" t="n">
-        <v>774</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115784</v>
+        <v>142126</v>
       </c>
       <c r="D4" t="n">
-        <v>2724</v>
+        <v>3020</v>
       </c>
       <c r="E4" t="n">
-        <v>483</v>
+        <v>431</v>
       </c>
       <c r="F4" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>142126</v>
+        <v>36040</v>
       </c>
       <c r="D6" t="n">
-        <v>3020</v>
+        <v>1528</v>
       </c>
       <c r="E6" t="n">
-        <v>431</v>
+        <v>212</v>
       </c>
       <c r="F6" t="n">
-        <v>382</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36040</v>
+        <v>69669</v>
       </c>
       <c r="D7" t="n">
-        <v>1528</v>
+        <v>2284</v>
       </c>
       <c r="E7" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28730</v>
+        <v>19824</v>
       </c>
       <c r="D8" t="n">
-        <v>1356</v>
+        <v>1156</v>
       </c>
       <c r="E8" t="n">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="F8" t="n">
-        <v>193</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19824</v>
+        <v>56420</v>
       </c>
       <c r="D9" t="n">
-        <v>1156</v>
+        <v>1908</v>
       </c>
       <c r="E9" t="n">
-        <v>177</v>
+        <v>282</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>28730</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1356</v>
+      </c>
+      <c r="E10" t="n">
+        <v>203</v>
+      </c>
+      <c r="F10" t="n">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/491.xlsx
+++ b/output/roomself_excel/491.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,12 +540,37 @@
       <c r="D2" t="n">
         <v>2724</v>
       </c>
-      <c r="E2" t="n">
-        <v>376</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>363</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>328</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +587,60 @@
       <c r="D3" t="n">
         <v>3756</v>
       </c>
-      <c r="E3" t="n">
-        <v>605</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>399</v>
+        <v>239</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>571</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>62</v>
+      </c>
+      <c r="M3" t="n">
+        <v>47</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>64</v>
+      </c>
+      <c r="P3" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>50</v>
+      </c>
+      <c r="S3" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +658,37 @@
       <c r="D4" t="n">
         <v>3020</v>
       </c>
-      <c r="E4" t="n">
-        <v>431</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>382</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>358</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +705,29 @@
       <c r="D5" t="n">
         <v>1132</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>113</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>23</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +744,29 @@
       <c r="D6" t="n">
         <v>1528</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>212</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>23</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +783,21 @@
       <c r="D7" t="n">
         <v>2284</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +814,29 @@
       <c r="D8" t="n">
         <v>1156</v>
       </c>
-      <c r="E8" t="n">
-        <v>177</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
+        <v>174</v>
+      </c>
+      <c r="G8" t="n">
         <v>34</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +853,37 @@
       <c r="D9" t="n">
         <v>1908</v>
       </c>
-      <c r="E9" t="n">
-        <v>282</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>239</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>520</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +900,37 @@
       <c r="D10" t="n">
         <v>1356</v>
       </c>
-      <c r="E10" t="n">
-        <v>203</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>193</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>170</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/491.xlsx
+++ b/output/roomself_excel/491.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,126 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_5</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_5</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_5</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_5</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_6</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_6</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_6</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_6</t>
         </is>
       </c>
     </row>
@@ -571,6 +691,42 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>180</v>
+      </c>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -641,6 +797,102 @@
       </c>
       <c r="S3" t="n">
         <v>47</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>186</v>
+      </c>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -689,6 +941,42 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>182</v>
+      </c>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -728,6 +1016,30 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -767,6 +1079,30 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -798,6 +1134,30 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -837,6 +1197,42 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>86</v>
+      </c>
+      <c r="W8" t="n">
+        <v>34</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -884,6 +1280,42 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>80</v>
+      </c>
+      <c r="W9" t="n">
+        <v>11</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -931,6 +1363,42 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>63</v>
+      </c>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
